--- a/data/s1/Aradas/archetypes/pop_archetypes_transport.xlsx
+++ b/data/s1/Aradas/archetypes/pop_archetypes_transport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s1\Aradas\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9F30D0-3157-4B32-84A4-9FF70D491338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD55E432-D312-4D95-B2FC-79FF283444F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="L3" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M3" s="2">
         <v>62.984000000000002</v>
@@ -858,7 +858,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="L4" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -940,7 +940,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="L5" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M5" s="2">
         <v>53.112000000000002</v>
@@ -1020,7 +1020,7 @@
         <v>0.05</v>
       </c>
       <c r="L6" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M6" s="2">
         <v>43.322000000000003</v>
@@ -1100,7 +1100,7 @@
         <v>2</v>
       </c>
       <c r="L7" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M7" s="7">
         <f>293.323/30</f>
@@ -1186,7 +1186,7 @@
         <v>2</v>
       </c>
       <c r="L8" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -1270,7 +1270,7 @@
         <v>2</v>
       </c>
       <c r="L9" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M9" s="7">
         <f>357.554/30</f>
@@ -1355,8 +1355,8 @@
       <c r="K10">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="L10">
-        <v>0</v>
+      <c r="L10" s="2">
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M10" s="2">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:XFD1 A1:I6 M2:XFD2 J2:J6 S4:XFD4 T4:T7 A10:L10 A11:XFD1048576">
+  <conditionalFormatting sqref="J1:XFD1 A1:I6 M2:XFD2 J2:J6 S4:XFD4 T4:T7 A10:K10 A11:XFD1048576">
     <cfRule type="cellIs" dxfId="7" priority="22" operator="equal">
       <formula>0</formula>
     </cfRule>

--- a/data/s1/Aradas/archetypes/pop_archetypes_transport.xlsx
+++ b/data/s1/Aradas/archetypes/pop_archetypes_transport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s1\Aradas\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD55E432-D312-4D95-B2FC-79FF283444F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F3776F-99D9-4E40-A573-B1094E6338BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="855" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -169,10 +169,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,22 +177,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -204,7 +187,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -221,76 +210,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -577,7 +505,7 @@
     <col min="10" max="10" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="7.88671875" customWidth="1"/>
     <col min="13" max="16" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="11.109375" style="5" customWidth="1"/>
+    <col min="17" max="18" width="11.109375" customWidth="1"/>
     <col min="19" max="19" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -589,47 +517,47 @@
     <col min="28" max="29" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>19</v>
       </c>
       <c r="O1" s="1" t="s">
@@ -638,16 +566,16 @@
       <c r="P1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>4</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>5</v>
       </c>
       <c r="U1" s="1" t="s">
@@ -656,16 +584,16 @@
       <c r="V1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>13</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -694,10 +622,10 @@
       <c r="J2">
         <v>1</v>
       </c>
-      <c r="K2" s="2">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2">
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="M2">
@@ -706,28 +634,28 @@
       <c r="N2">
         <v>0</v>
       </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="5">
-        <v>0</v>
-      </c>
-      <c r="R2" s="5">
-        <v>0</v>
-      </c>
-      <c r="S2" s="8">
-        <v>0</v>
-      </c>
-      <c r="T2" s="8">
-        <v>0</v>
-      </c>
-      <c r="U2" s="8">
-        <v>0</v>
-      </c>
-      <c r="V2" s="8">
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>0</v>
+      </c>
+      <c r="R2" s="1">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2" s="1">
+        <v>0</v>
+      </c>
+      <c r="V2" s="1">
         <v>0</v>
       </c>
       <c r="W2">
@@ -762,10 +690,10 @@
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>36</v>
       </c>
       <c r="I3">
@@ -774,41 +702,41 @@
       <c r="J3">
         <v>0.1</v>
       </c>
-      <c r="K3" s="2">
-        <v>4.2999999999999997E-2</v>
-      </c>
-      <c r="L3" s="2">
+      <c r="K3" s="1">
+        <v>7.5499999999999998E-2</v>
+      </c>
+      <c r="L3">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3">
         <v>62.984000000000002</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3">
         <v>2.94</v>
       </c>
-      <c r="O3" s="2">
-        <v>2.6709999999999998</v>
-      </c>
-      <c r="P3" s="2">
-        <v>0.13800000000000001</v>
-      </c>
-      <c r="Q3" s="6">
+      <c r="O3" s="1">
+        <v>2.6360000000000001</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0.128</v>
+      </c>
+      <c r="Q3" s="1">
         <v>9999</v>
       </c>
-      <c r="R3" s="5">
-        <v>0</v>
-      </c>
-      <c r="S3" s="8">
-        <v>0</v>
-      </c>
-      <c r="T3" s="8">
-        <v>0</v>
-      </c>
-      <c r="U3" s="8">
-        <v>177.70699999999999</v>
-      </c>
-      <c r="V3" s="8">
-        <v>14.922000000000001</v>
+      <c r="R3" s="1">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3" s="1">
+        <v>177.58600000000001</v>
+      </c>
+      <c r="V3" s="1">
+        <v>13.057</v>
       </c>
       <c r="W3">
         <v>0</v>
@@ -842,10 +770,10 @@
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" t="s">
         <v>37</v>
       </c>
       <c r="I4">
@@ -854,10 +782,10 @@
       <c r="J4">
         <v>0.1</v>
       </c>
-      <c r="K4" s="2">
-        <v>9.7000000000000003E-2</v>
-      </c>
-      <c r="L4" s="2">
+      <c r="K4" s="1">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="L4">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="M4">
@@ -866,30 +794,30 @@
       <c r="N4">
         <v>0</v>
       </c>
-      <c r="O4" s="2">
-        <v>0.83899999999999997</v>
-      </c>
-      <c r="P4" s="2">
-        <v>5.6000000000000001E-2</v>
-      </c>
-      <c r="Q4" s="6">
+      <c r="O4" s="1">
+        <v>0.82699999999999996</v>
+      </c>
+      <c r="P4" s="1">
+        <v>3.9E-2</v>
+      </c>
+      <c r="Q4" s="1">
         <v>9999</v>
       </c>
-      <c r="R4" s="5">
-        <v>0</v>
-      </c>
-      <c r="S4" s="9">
+      <c r="R4" s="1">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <f>O4*0.5</f>
-        <v>0.41949999999999998</v>
-      </c>
-      <c r="T4" s="9">
+        <v>0.41349999999999998</v>
+      </c>
+      <c r="T4">
         <f>P4*0.5</f>
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="U4" s="8">
-        <v>0</v>
-      </c>
-      <c r="V4" s="8">
+        <v>1.95E-2</v>
+      </c>
+      <c r="U4" s="1">
+        <v>0</v>
+      </c>
+      <c r="V4" s="1">
         <v>0</v>
       </c>
       <c r="W4">
@@ -924,10 +852,10 @@
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" t="s">
         <v>36</v>
       </c>
       <c r="I5">
@@ -936,41 +864,41 @@
       <c r="J5">
         <v>0.1</v>
       </c>
-      <c r="K5" s="2">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="L5" s="2">
+      <c r="K5" s="1">
+        <v>7.5499999999999998E-2</v>
+      </c>
+      <c r="L5">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5">
         <v>53.112000000000002</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5">
         <v>3.9049999999999998</v>
       </c>
-      <c r="O5" s="2">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="P5" s="2">
-        <v>0.17799999999999999</v>
-      </c>
-      <c r="Q5" s="6">
+      <c r="O5" s="1">
+        <v>2.2759999999999998</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0.159</v>
+      </c>
+      <c r="Q5" s="1">
         <v>9999</v>
       </c>
-      <c r="R5" s="5">
-        <v>0</v>
-      </c>
-      <c r="S5" s="8">
-        <v>0</v>
-      </c>
-      <c r="T5" s="8">
-        <v>0</v>
-      </c>
-      <c r="U5" s="8">
-        <v>146.732</v>
-      </c>
-      <c r="V5" s="8">
-        <v>20.474</v>
+      <c r="R5" s="1">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5" s="1">
+        <v>153.46100000000001</v>
+      </c>
+      <c r="V5" s="1">
+        <v>21.074999999999999</v>
       </c>
       <c r="W5">
         <v>0</v>
@@ -1004,10 +932,10 @@
       <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" t="s">
         <v>36</v>
       </c>
       <c r="I6">
@@ -1016,41 +944,41 @@
       <c r="J6">
         <v>0.1</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6">
         <v>0.05</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6">
         <v>43.322000000000003</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6">
         <v>2.206</v>
       </c>
-      <c r="O6" s="2">
-        <v>1.9750000000000001</v>
-      </c>
-      <c r="P6" s="2">
-        <v>0.20399999999999999</v>
-      </c>
-      <c r="Q6" s="6">
+      <c r="O6" s="1">
+        <v>2.089</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="Q6" s="1">
         <v>9999</v>
       </c>
-      <c r="R6" s="5">
-        <v>0</v>
-      </c>
-      <c r="S6" s="8">
-        <v>0</v>
-      </c>
-      <c r="T6" s="8">
-        <v>0</v>
-      </c>
-      <c r="U6" s="8">
-        <v>37.835000000000001</v>
-      </c>
-      <c r="V6" s="8">
-        <v>60.267000000000003</v>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1">
+        <v>45.908999999999999</v>
+      </c>
+      <c r="V6" s="1">
+        <v>61.256</v>
       </c>
       <c r="W6">
         <v>0</v>
@@ -1084,10 +1012,10 @@
       <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" t="s">
         <v>35</v>
       </c>
       <c r="I7">
@@ -1096,47 +1024,48 @@
       <c r="J7">
         <v>0.1</v>
       </c>
-      <c r="K7" s="2">
-        <v>2</v>
-      </c>
-      <c r="L7" s="2">
+      <c r="K7" s="1">
+        <f>4/21*0.9</f>
+        <v>0.17142857142857143</v>
+      </c>
+      <c r="L7">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7">
         <f>293.323/30</f>
         <v>9.7774333333333328</v>
       </c>
-      <c r="N7" s="7">
+      <c r="N7">
         <f>38.284/30</f>
         <v>1.2761333333333333</v>
       </c>
-      <c r="O7" s="7">
-        <f>12.372/30</f>
-        <v>0.41239999999999999</v>
-      </c>
-      <c r="P7" s="7">
-        <f>1.668/30</f>
-        <v>5.5599999999999997E-2</v>
-      </c>
-      <c r="Q7" s="6">
+      <c r="O7" s="2">
+        <f>13.877/45</f>
+        <v>0.30837777777777781</v>
+      </c>
+      <c r="P7" s="2">
+        <f>1.793/45</f>
+        <v>3.9844444444444446E-2</v>
+      </c>
+      <c r="Q7" s="1">
         <v>9999</v>
       </c>
-      <c r="R7" s="5">
-        <v>0</v>
-      </c>
-      <c r="S7" s="8">
-        <v>0</v>
-      </c>
-      <c r="T7" s="8">
-        <v>0</v>
-      </c>
-      <c r="U7" s="8">
-        <f>740.509/30</f>
-        <v>24.683633333333333</v>
-      </c>
-      <c r="V7" s="8">
-        <f>271.113/30</f>
-        <v>9.0371000000000006</v>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2">
+        <f>836.791/45</f>
+        <v>18.595355555555557</v>
+      </c>
+      <c r="V7" s="2">
+        <f>296.405/45</f>
+        <v>6.586777777777777</v>
       </c>
       <c r="W7">
         <v>0</v>
@@ -1170,10 +1099,10 @@
       <c r="F8">
         <v>1</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" t="s">
         <v>37</v>
       </c>
       <c r="I8">
@@ -1182,10 +1111,11 @@
       <c r="J8">
         <v>0.1</v>
       </c>
-      <c r="K8" s="2">
-        <v>2</v>
-      </c>
-      <c r="L8" s="2">
+      <c r="K8" s="1">
+        <f t="shared" ref="K8:K9" si="0">4/21*0.9</f>
+        <v>0.17142857142857143</v>
+      </c>
+      <c r="L8">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="M8">
@@ -1195,31 +1125,31 @@
         <v>0</v>
       </c>
       <c r="O8" s="2">
-        <f>5.542/30</f>
-        <v>0.18473333333333333</v>
+        <f>5.657/45</f>
+        <v>0.12571111111111111</v>
       </c>
       <c r="P8" s="2">
-        <f>1.704/30</f>
-        <v>5.6799999999999996E-2</v>
-      </c>
-      <c r="Q8" s="6">
+        <f>1.622/45</f>
+        <v>3.6044444444444448E-2</v>
+      </c>
+      <c r="Q8" s="1">
         <v>9999</v>
       </c>
-      <c r="R8" s="5">
-        <v>0</v>
-      </c>
-      <c r="S8" s="9">
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <f>O8*0.5</f>
-        <v>9.2366666666666666E-2</v>
-      </c>
-      <c r="T8" s="9">
+        <v>6.2855555555555553E-2</v>
+      </c>
+      <c r="T8">
         <f>P8*0.5</f>
-        <v>2.8399999999999998E-2</v>
-      </c>
-      <c r="U8" s="8">
-        <v>0</v>
-      </c>
-      <c r="V8" s="8">
+        <v>1.8022222222222224E-2</v>
+      </c>
+      <c r="U8" s="2">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2">
         <v>0</v>
       </c>
       <c r="W8">
@@ -1254,10 +1184,10 @@
       <c r="F9">
         <v>1</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" t="s">
         <v>35</v>
       </c>
       <c r="I9">
@@ -1266,47 +1196,44 @@
       <c r="J9">
         <v>0.1</v>
       </c>
-      <c r="K9" s="2">
-        <v>2</v>
-      </c>
-      <c r="L9" s="2">
+      <c r="K9" s="1">
+        <f t="shared" si="0"/>
+        <v>0.17142857142857143</v>
+      </c>
+      <c r="L9">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9">
         <f>357.554/30</f>
         <v>11.918466666666665</v>
       </c>
-      <c r="N9" s="7">
+      <c r="N9">
         <f>68.396/30</f>
         <v>2.2798666666666665</v>
       </c>
-      <c r="O9" s="7">
-        <f>16.118/30</f>
-        <v>0.53726666666666667</v>
-      </c>
-      <c r="P9" s="7">
-        <f>2.637/30</f>
-        <v>8.7900000000000006E-2</v>
-      </c>
-      <c r="Q9" s="6">
+      <c r="O9" s="1">
+        <v>16.956</v>
+      </c>
+      <c r="P9" s="1">
+        <v>2.524</v>
+      </c>
+      <c r="Q9" s="1">
         <v>9999</v>
       </c>
-      <c r="R9" s="5">
-        <v>0</v>
-      </c>
-      <c r="S9" s="8">
-        <v>0</v>
-      </c>
-      <c r="T9" s="8">
-        <v>0</v>
-      </c>
-      <c r="U9" s="8">
-        <f>411.627/30</f>
-        <v>13.7209</v>
-      </c>
-      <c r="V9" s="8">
-        <f>386.868/30</f>
-        <v>12.8956</v>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9" s="1">
+        <v>472.11500000000001</v>
+      </c>
+      <c r="V9" s="1">
+        <v>376.47300000000001</v>
       </c>
       <c r="W9">
         <v>0</v>
@@ -1352,28 +1279,28 @@
       <c r="J10">
         <v>0.1</v>
       </c>
-      <c r="K10">
-        <v>9.7000000000000003E-2</v>
-      </c>
-      <c r="L10" s="2">
+      <c r="K10" s="1">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="L10">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M10" s="2">
-        <v>0</v>
-      </c>
-      <c r="N10" s="2">
-        <v>0</v>
-      </c>
-      <c r="O10" s="2">
-        <v>0.83899999999999997</v>
-      </c>
-      <c r="P10" s="2">
-        <v>5.6000000000000001E-2</v>
-      </c>
-      <c r="Q10" s="6">
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0.82699999999999996</v>
+      </c>
+      <c r="P10" s="1">
+        <v>3.9E-2</v>
+      </c>
+      <c r="Q10" s="1">
         <v>9999</v>
       </c>
-      <c r="R10" s="5">
+      <c r="R10" s="1">
         <v>0</v>
       </c>
       <c r="S10">
@@ -1382,10 +1309,10 @@
       <c r="T10">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
+      <c r="U10" s="1">
+        <v>0</v>
+      </c>
+      <c r="V10" s="1">
         <v>0</v>
       </c>
       <c r="W10">
@@ -1402,51 +1329,6 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:J9">
-    <cfRule type="cellIs" dxfId="8" priority="17" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:XFD1 A1:I6 M2:XFD2 J2:J6 S4:XFD4 T4:T7 A10:K10 A11:XFD1048576">
-    <cfRule type="cellIs" dxfId="7" priority="22" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M4:P4">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M7:P8">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O3:XFD3">
-    <cfRule type="cellIs" dxfId="4" priority="9" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q4:R10">
-    <cfRule type="cellIs" dxfId="3" priority="19" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S7">
-    <cfRule type="cellIs" dxfId="2" priority="15" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S8:T10">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U5:XFD10">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/data/s1/Aradas/archetypes/pop_archetypes_transport.xlsx
+++ b/data/s1/Aradas/archetypes/pop_archetypes_transport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s1\Aradas\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F3776F-99D9-4E40-A573-B1094E6338BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED99E33F-FC61-4A6D-8A03-F11AAA496FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="855" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -178,7 +178,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -197,6 +197,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -210,10 +216,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1279,8 +1286,8 @@
       <c r="J10">
         <v>0.1</v>
       </c>
-      <c r="K10" s="1">
-        <v>0.20499999999999999</v>
+      <c r="K10" s="3">
+        <v>1.2394195888754533</v>
       </c>
       <c r="L10">
         <v>1.0000000000000001E-5</v>
